--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484852_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484852_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.26</v>
+        <v>5.0216</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8009</v>
+        <v>3.3209</v>
       </c>
       <c r="F2" t="n">
-        <v>2.459</v>
+        <v>1.7007</v>
       </c>
       <c r="G2" t="n">
         <v>6.5909</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4812</v>
+        <v>2.2428</v>
       </c>
       <c r="T2" t="n">
-        <v>2.567</v>
+        <v>1.087</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9142</v>
+        <v>1.1558</v>
       </c>
       <c r="V2" t="n">
         <v>1.8488</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2972</v>
+        <v>4.7172</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9769</v>
+        <v>1.5557</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3203</v>
+        <v>3.1615</v>
       </c>
       <c r="G3" t="n">
         <v>2.4809</v>
@@ -688,13 +688,13 @@
         <v>2.0757</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6464</v>
+        <v>2.0664</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5206</v>
+        <v>1.0993</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1258</v>
+        <v>0.9671</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9624</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1509</v>
+        <v>3.3773</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2674</v>
+        <v>2.5467</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8835</v>
+        <v>0.8306</v>
       </c>
       <c r="G4" t="n">
         <v>3.6833</v>
@@ -766,13 +766,13 @@
         <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8641</v>
+        <v>1.0905</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6671</v>
+        <v>0.9464</v>
       </c>
       <c r="U4" t="n">
-        <v>0.197</v>
+        <v>0.1441</v>
       </c>
       <c r="V4" t="n">
         <v>0.3018</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6619</v>
+        <v>1.4767</v>
       </c>
       <c r="E5" t="n">
         <v>0.4092</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2527</v>
+        <v>1.0675</v>
       </c>
       <c r="G5" t="n">
         <v>0.8577</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4644</v>
+        <v>0.2792</v>
       </c>
       <c r="T5" t="n">
         <v>0.0711</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3933</v>
+        <v>0.2081</v>
       </c>
       <c r="V5" t="n">
         <v>0.3398</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0243</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3079</v>
+        <v>-0.6057</v>
       </c>
       <c r="F7" t="n">
         <v>1.2836</v>
@@ -1000,10 +1000,10 @@
         <v>1.5096</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2598</v>
+        <v>0.4424</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.458</v>
+        <v>0.2442</v>
       </c>
       <c r="U7" t="n">
         <v>0.1981</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2414</v>
+        <v>-0.8572</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2841</v>
+        <v>-1.8998</v>
       </c>
       <c r="F8" t="n">
         <v>1.0427</v>
@@ -1078,10 +1078,10 @@
         <v>2.0757</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7207</v>
+        <v>0.6635</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.786</v>
+        <v>0.5982</v>
       </c>
       <c r="U8" t="n">
         <v>0.0653</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9615</v>
+        <v>-2.9057</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6603</v>
+        <v>-2.7632</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3012</v>
+        <v>-0.1425</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5135</v>
@@ -1156,13 +1156,13 @@
         <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8253</v>
+        <v>0.2304</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4456</v>
+        <v>0.4514</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3797</v>
+        <v>-0.221</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1299</v>
+        <v>-3.6005</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.4173</v>
+        <v>-6.364</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2873</v>
+        <v>2.7635</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6561</v>
@@ -1234,13 +1234,13 @@
         <v>1.887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3415</v>
+        <v>1.1879</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6808</v>
+        <v>0.3725</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3392</v>
+        <v>0.8154</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3018</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9806</v>
+        <v>-6.4594</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7471</v>
+        <v>-5.3317</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2335</v>
+        <v>-1.1277</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6555</v>
@@ -1312,13 +1312,13 @@
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1469</v>
+        <v>0.6681</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5031</v>
+        <v>0.9185</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3562</v>
+        <v>-0.2504</v>
       </c>
       <c r="V11" t="n">
         <v>-1.585</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.2832</v>
+        <v>2.698800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.7114</v>
+        <v>-7.881</v>
       </c>
       <c r="F12" t="n">
-        <v>10.9944</v>
+        <v>10.5799</v>
       </c>
       <c r="G12" t="n">
         <v>3.7342</v>
@@ -1390,13 +1390,13 @@
         <v>13.209</v>
       </c>
       <c r="S12" t="n">
-        <v>9.455700000000002</v>
+        <v>8.8712</v>
       </c>
       <c r="T12" t="n">
-        <v>5.958500000000001</v>
+        <v>5.7886</v>
       </c>
       <c r="U12" t="n">
-        <v>3.497</v>
+        <v>3.0825</v>
       </c>
       <c r="V12" t="n">
         <v>-1.604</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MADINYH EGEA</t>
+          <t>A. SERNEGUET GARVI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.609</v>
+        <v>2.4274</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9422</v>
+        <v>0.581</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3332</v>
+        <v>1.8464</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2542</v>
+        <v>1.3034</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6738</v>
+        <v>1.2467</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5803</v>
+        <v>0.0567</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0896</v>
+        <v>1.9825</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0074</v>
+        <v>2.4675</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0823</v>
+        <v>-0.485</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8354</v>
+        <v>-0.6791</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3335</v>
+        <v>-1.2208</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4981</v>
+        <v>0.5417</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4531</v>
+        <v>0.9435</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6418</v>
+        <v>3.0192</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4867</v>
+        <v>-1.3664</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0792</v>
+        <v>-0.8727</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5925</v>
+        <v>-0.4937</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.585</v>
+        <v>1.547</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.038</v>
+        <v>1.547</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SERNEGUET GARVI</t>
+          <t>J. MADINYH EGEA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2967</v>
+        <v>2.0448</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0036</v>
+        <v>2.0653</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3003</v>
+        <v>-0.0204</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3034</v>
+        <v>1.2542</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2467</v>
+        <v>0.6738</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0567</v>
+        <v>0.5803</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9825</v>
+        <v>2.0896</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4675</v>
+        <v>2.0074</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.485</v>
+        <v>0.0823</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6791</v>
+        <v>-0.8354</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2208</v>
+        <v>-1.3335</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5417</v>
+        <v>0.4981</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9435</v>
+        <v>2.4531</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0757</v>
+        <v>-0.1887</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0192</v>
+        <v>2.6418</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.4971</v>
+        <v>-0.0775</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4574</v>
+        <v>0.2023</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0398</v>
+        <v>-0.2798</v>
       </c>
       <c r="V14" t="n">
-        <v>1.547</v>
+        <v>-1.585</v>
       </c>
       <c r="W14" t="n">
-        <v>1.547</v>
+        <v>-0.038</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6701</v>
+        <v>1.7261</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.873</v>
+        <v>-0.2884</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5431</v>
+        <v>2.0146</v>
       </c>
       <c r="G15" t="n">
         <v>0.9143</v>
@@ -1624,13 +1624,13 @@
         <v>3.0192</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0181</v>
+        <v>-0.962</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1758</v>
+        <v>-0.5911</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8423</v>
+        <v>-0.3709</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3018</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ORTIN GOMEZ</t>
+          <t>I. DURAN OLMOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2785</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2447</v>
+        <v>0.6949</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0339</v>
+        <v>-0.0917</v>
       </c>
       <c r="G16" t="n">
-        <v>0.552</v>
+        <v>0.7703</v>
       </c>
       <c r="H16" t="n">
-        <v>0.695</v>
+        <v>1.8548</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.143</v>
+        <v>-1.0844</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.9395</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3946</v>
+        <v>2.1975</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.641</v>
+        <v>-1.258</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2015</v>
+        <v>-0.1692</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6996</v>
+        <v>-0.3428</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4981</v>
+        <v>0.1736</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0757</v>
+        <v>1.6983</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.104</v>
+        <v>-0.6202</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8107</v>
+        <v>-0.0559</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2933</v>
+        <v>-0.5643</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2452</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.547</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. DURAN OLMOS</t>
+          <t>A. ORTIN GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1568</v>
+        <v>0.4181</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6949</v>
+        <v>0.4395</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8518</v>
+        <v>-0.0214</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7703</v>
+        <v>0.552</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8548</v>
+        <v>0.695</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0844</v>
+        <v>-0.143</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9395</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1975</v>
+        <v>1.3946</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.258</v>
+        <v>-0.641</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1692</v>
+        <v>-0.2015</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3428</v>
+        <v>-0.6996</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1736</v>
+        <v>0.4981</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6983</v>
+        <v>2.0757</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3803</v>
+        <v>-0.9644</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0559</v>
+        <v>-0.6158</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3244</v>
+        <v>-0.3485</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2452</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2452</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7825</v>
+        <v>-0.3566</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.1952</v>
+        <v>-4.0004</v>
       </c>
       <c r="F18" t="n">
-        <v>3.4128</v>
+        <v>3.6438</v>
       </c>
       <c r="G18" t="n">
         <v>-3.2101</v>
@@ -1858,13 +1858,13 @@
         <v>3.5853</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1575</v>
+        <v>-0.7316</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.749</v>
+        <v>-0.5541</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4084</v>
+        <v>-0.1774</v>
       </c>
       <c r="V18" t="n">
         <v>1.8868</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8503</v>
+        <v>-1.4582</v>
       </c>
       <c r="E19" t="n">
         <v>-1.666</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1843</v>
+        <v>0.2078</v>
       </c>
       <c r="G19" t="n">
         <v>-2.9144</v>
@@ -1936,13 +1936,13 @@
         <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3698</v>
+        <v>0.0223</v>
       </c>
       <c r="T19" t="n">
         <v>0.0029</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3727</v>
+        <v>0.0194</v>
       </c>
       <c r="V19" t="n">
         <v>1.2452</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.834</v>
+        <v>-2.7125</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9361</v>
+        <v>-2.8387</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1021</v>
+        <v>0.1262</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6864</v>
@@ -2014,13 +2014,13 @@
         <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.355</v>
+        <v>-0.2335</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2816</v>
+        <v>-0.1842</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0493</v>
       </c>
       <c r="V20" t="n">
         <v>0.6606</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9928</v>
+        <v>-3.8563</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.3965</v>
+        <v>-7.1759</v>
       </c>
       <c r="F21" t="n">
-        <v>3.4037</v>
+        <v>3.3196</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9884</v>
@@ -2092,13 +2092,13 @@
         <v>3.5853</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4297</v>
+        <v>-0.4338</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.2417</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1081</v>
+        <v>-0.1921</v>
       </c>
       <c r="V21" t="n">
         <v>0.6415999999999999</v>
@@ -2125,25 +2125,25 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7621</v>
+        <v>-1.163900000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.1886</v>
+        <v>-12.1887</v>
       </c>
       <c r="F22" t="n">
-        <v>8.426600000000001</v>
+        <v>11.0249</v>
       </c>
       <c r="G22" t="n">
         <v>-4.005100000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9486</v>
+        <v>-1.948600000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0565</v>
+        <v>-2.056500000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6109999999999993</v>
+        <v>0.6109999999999989</v>
       </c>
       <c r="K22" t="n">
         <v>6.6754</v>
@@ -2170,13 +2170,13 @@
         <v>21.7005</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.965399999999999</v>
+        <v>-5.3671</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.9105</v>
+        <v>-2.9103</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.0549</v>
+        <v>-2.4566</v>
       </c>
       <c r="V22" t="n">
         <v>1.604</v>
